--- a/outputs/Redditch Library - Fenster Take-Off and Benchmark Price.xlsx
+++ b/outputs/Redditch Library - Fenster Take-Off and Benchmark Price.xlsx
@@ -12,6 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmark Price" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inclusions &amp; Exclusions" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RFIs &amp; Queries" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Margin &amp; Confidence" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2222,7 +2223,7 @@
       <c r="C45" s="5" t="inlineStr"/>
       <c r="D45" s="5" t="inlineStr"/>
       <c r="E45" s="5" t="n">
-        <v>136.54</v>
+        <v>136.53</v>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
@@ -4090,7 +4091,7 @@
       <c r="E48" s="5" t="inlineStr"/>
       <c r="F48" s="5" t="inlineStr"/>
       <c r="G48" s="5" t="n">
-        <v>1814.56</v>
+        <v>1814.51</v>
       </c>
       <c r="H48" s="5" t="inlineStr"/>
       <c r="I48" s="5" t="inlineStr"/>
@@ -4112,7 +4113,7 @@
       <c r="E49" s="1" t="inlineStr"/>
       <c r="F49" s="1" t="inlineStr"/>
       <c r="G49" s="1" t="n">
-        <v>89910.82000000001</v>
+        <v>89910.77</v>
       </c>
       <c r="H49" s="1" t="inlineStr"/>
       <c r="I49" s="1" t="inlineStr"/>
@@ -4691,4 +4692,407 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="74" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Redditch Library - what we keep, and how sure I am of it</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>WHAT THE BENCHMARK IS MADE OF</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr"/>
+      <c r="C2" s="5" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Frame supply - COST</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>60551.26</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>What a supplier would charge us. Benchmark, not a quotation - nobody has been asked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Solar-control glass premium - COST</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1814.51</v>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>The specified outer pane is 4mm bronze anti-sun; the frame rates are built from ordinary softcoat units.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5">
+        <f> Material we buy</f>
+        <v/>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>62365.77</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>House code adders - MARGIN</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>19875</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>The template's per-unit adder at 75% of code value. This is the money we keep on materials.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Installation - revenue</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>7670</v>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Adam's per-unit labour codes. FIT ONLY. What fitting actually costs Fenster is recorded nowhere, so this is revenue and not margin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>89910.77</v>
+      </c>
+      <c r="C8" s="1" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Gross margin if fitting breaks even</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>19875</v>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>22.1% of sell, 31.9% mark-up on the material buy. NOT net profit - no prelims, supervision, survey, main contractor's discount or strip-out are in it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>WHY THE MARGIN IS THIN HERE</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>The house adder is a FIXED SUM PER UNIT, so it thins as units get bigger.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  &lt;1.5m2 - 11 items</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>3712.5</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>adder is 50.7% of the frame line</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  1.5-3m2 - 10 items</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>5700</v>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>adder is 38.6% of the frame line</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  3-6m2 - 20 items</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>9337.5</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>adder is 19.0% of the frame line</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  &gt;6m2 - 2 items</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>1125</v>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>adder is 12.2% of the frame line</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Redditch averages 3.18 m2 a unit</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>adder = 24.7% of the frame line. Crestwood Park averaged 1.29 m2 and the adder was 42.9% (GBP 20,550 on a GBP 27,329.60 BSW buy). Big units earn less on this template.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>CONFIDENCE - AGAINST A REAL COMPARABLE BUY</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>BSW QT250834, 15/06/2026, Pride Developments - Severn Trent. Sheerline Prestige aluminium casements, factory glazed, trickle vents, shootbolt locking - the nearest thing Fenster holds to this job. 6 lines, 27 units, 72.578 m2, reconciling exactly to their stated Total Nett Ex VAT of GBP 34,902.35.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Fitted rate curve</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr"/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>rate = 721.47 x area^-0.4093, R2 = 0.9934. Two caveats, both pushing it HIGH for our purposes: that job is 3005 Wine Red metallic, and its outer pane is 6.8 laminated rather than 4mm toughened.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>THREE ESTIMATES OF THE SAME JOB</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Engine benchmark (as issued)</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>89910.77</v>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>Register and learned medians through mary_pricing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Re-priced on the Severn Trent curve</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>86354.89</v>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Same supplier, same client, six weeks old, same product family. The best single comparator we have.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  St Mary's band correction</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>79047.5</v>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>The engine's measured band errors from the St Mary's calibration applied to the supply component.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Spread</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>10863.27</v>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>Almost entirely the 3-6 m2 band, which carries 62% of this job.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>CAN WE UNDERCUT JOEDAN?</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr"/>
+      <c r="C27" s="5" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Joedan gross of 2.5% MCD</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>90687.17</v>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Their quotation JCQ.9727 as it sits in the tender pack.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Joedan NET to a main contractor</t>
+        </is>
+      </c>
+      <c r="B29" s="1" t="n">
+        <v>88419.99000000001</v>
+      </c>
+      <c r="C29" s="1" t="inlineStr">
+        <is>
+          <t>THE NUMBER TO BEAT - and it INCLUDES their strip-out (their cl.12). Ours does not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Headroom at the engine benchmark</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>-1490.78</v>
+      </c>
+      <c r="C30" s="4">
+        <f> GBP -34.67 per opening towards stripping 43 openings out of an occupied library.</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Headroom on the Severn Trent curve</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>2065.1</v>
+      </c>
+      <c r="C31" s="3">
+        <f> GBP 48.03 per opening towards stripping 43 openings out of an occupied library.</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Headroom on the band correction</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>9372.5</v>
+      </c>
+      <c r="C32" s="3">
+        <f> GBP 217.97 per opening towards stripping 43 openings out of an occupied library.</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>